--- a/data/trans_camb/P32B-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P32B-Habitat-trans_camb.xlsx
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 2,72</t>
+          <t>-0,34; 2,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 2,22</t>
+          <t>-1,04; 2,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 0,72</t>
+          <t>-1,73; 0,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -697,27 +697,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 1,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>0,0; 3,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,93</t>
+          <t>-0,21; 2,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,75</t>
+          <t>-0,49; 1,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 0,83</t>
+          <t>-0,86; 0,86</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-49,75; 1167,13</t>
+          <t>-59,32; 1047,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-56,31; 1080,03</t>
+          <t>-47,08; 1178,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,31; 1251,28</t>
+          <t>-73,54; 927,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 3,11</t>
+          <t>-0,04; 2,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,15</t>
+          <t>0,65; 4,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 4,13</t>
+          <t>0,31; 4,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,15</t>
+          <t>-1,93; 1,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,18</t>
+          <t>-1,87; 0,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 4,85</t>
+          <t>-0,1; 4,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 1,94</t>
+          <t>-0,21; 1,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,71</t>
+          <t>0,21; 2,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,61</t>
+          <t>0,62; 3,63</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-22,55; 849,4</t>
+          <t>-23,35; 696,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,32; 1455,84</t>
+          <t>19,33; 1280,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 1252,04</t>
+          <t>-11,09; 1163,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,99; —</t>
+          <t>-59,73; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,0; 472,14</t>
+          <t>-25,68; 459,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,48; 651,82</t>
+          <t>3,39; 587,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27,15; 766,77</t>
+          <t>35,0; 801,0</t>
         </is>
       </c>
     </row>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 4,08</t>
+          <t>0,25; 4,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,72</t>
+          <t>-1,18; 1,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 1,47</t>
+          <t>-1,28; 1,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 3,91</t>
+          <t>0,04; 3,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,9</t>
+          <t>0,26; 2,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,95</t>
+          <t>-0,95; 1,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,74</t>
+          <t>-0,65; 1,61</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,24; —</t>
+          <t>-10,57; 1547,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-89,93; —</t>
+          <t>-94,3; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 1380,15</t>
+          <t>-25,46; 1192,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-81,49; —</t>
+          <t>-77,48; 1010,84</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 6,19</t>
+          <t>1,89; 6,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,25</t>
+          <t>0,35; 3,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,68</t>
+          <t>0,56; 4,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 0,61</t>
+          <t>-3,28; 0,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 2,03</t>
+          <t>-2,42; 2,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 0,46</t>
+          <t>-3,37; 0,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,25</t>
+          <t>0,38; 3,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 2,22</t>
+          <t>-0,28; 2,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 2,4</t>
+          <t>-0,44; 2,44</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>105,27; 2657,4</t>
+          <t>86,04; 2381,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-15,45; 1005,19</t>
+          <t>-0,41; 1243,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-16,49; 1404,1</t>
+          <t>5,18; 2159,64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-89,67; 99,68</t>
+          <t>-89,84; 124,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-69,46; 206,35</t>
+          <t>-70,12; 187,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-87,99; 77,99</t>
+          <t>-89,0; 65,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,83; 358,77</t>
+          <t>4,7; 407,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 272,3</t>
+          <t>-19,54; 306,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-32,56; 283,93</t>
+          <t>-26,72; 297,43</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,86</t>
+          <t>1,2; 3,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,09</t>
+          <t>0,51; 2,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,13</t>
+          <t>0,33; 2,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,4</t>
+          <t>-1,23; 0,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 0,83</t>
+          <t>-0,92; 0,86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,39</t>
+          <t>-0,82; 1,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,96</t>
+          <t>0,59; 1,88</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,4</t>
+          <t>0,23; 1,42</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,57</t>
+          <t>0,08; 1,54</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>91,38; 537,71</t>
+          <t>92,96; 543,63</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>40,23; 377,81</t>
+          <t>38,4; 393,79</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21,08; 381,53</t>
+          <t>20,03; 366,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-81,27; 79,7</t>
+          <t>-78,24; 100,15</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-63,65; 154,89</t>
+          <t>-61,33; 169,78</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-50,68; 231,18</t>
+          <t>-52,38; 214,67</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,47; 284,25</t>
+          <t>48,87; 288,83</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>17,34; 215,81</t>
+          <t>16,6; 224,96</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5,11; 233,72</t>
+          <t>5,96; 229,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P32B-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P32B-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>-0,28</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,03</t>
         </is>
       </c>
     </row>
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,85</t>
+          <t>-0,34; 2,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 2,01</t>
+          <t>-0,92; 2,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,71</t>
+          <t>-1,69; 0,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -697,27 +697,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,82</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 2,07</t>
+          <t>-0,31; 1,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,61</t>
+          <t>-0,52; 1,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,86</t>
+          <t>-1,01; 0,76</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-30,61%</t>
+          <t>-33,8%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -783,42 +783,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-59,32; 1047,65</t>
+          <t>-54,0; 1174,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>-82,45; 910,73</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-47,08; 1178,03</t>
+          <t>-54,11; 1157,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-73,54; 927,76</t>
+          <t>-66,5; 873,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,88</t>
+          <t>1,76</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,83</t>
+          <t>1,67</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 2,93</t>
+          <t>0,04; 3,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,15</t>
+          <t>0,76; 4,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,53</t>
+          <t>0,18; 3,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 1,02</t>
+          <t>-1,92; 1,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,91</t>
+          <t>-1,88; 0,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 4,66</t>
+          <t>-0,25; 4,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1,97</t>
+          <t>-0,19; 2,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,62</t>
+          <t>0,3; 2,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,63</t>
+          <t>0,36; 3,29</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>216,39%</t>
+          <t>193,78%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>234,96%</t>
+          <t>220,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>222,14%</t>
+          <t>202,01%</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,35; 696,71</t>
+          <t>-15,06; 747,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,33; 1280,27</t>
+          <t>33,67; 1104,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 1163,57</t>
+          <t>-25,3; 798,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-59,73; —</t>
+          <t>-77,44; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-25,68; 459,21</t>
+          <t>-30,61; 489,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 587,32</t>
+          <t>13,39; 625,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>35,0; 801,0</t>
+          <t>9,11; 705,19</t>
         </is>
       </c>
     </row>
@@ -1066,37 +1066,37 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>1,03</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,48</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0,02</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,48</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,02</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>1,46</t>
         </is>
       </c>
     </row>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 4,06</t>
+          <t>0,25; 3,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,66</t>
+          <t>-1,17; 1,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,37</t>
+          <t>-0,55; 3,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,41</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 3,89</t>
+          <t>0,71; 6,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,96</t>
+          <t>0,32; 2,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,02</t>
+          <t>-0,88; 0,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,61</t>
+          <t>0,13; 3,47</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>127,77%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>252,45%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 1547,14</t>
+          <t>-12,95; 1308,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-94,3; —</t>
+          <t>-75,83; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-25,46; 1192,52</t>
+          <t>-5,38; 1550,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-77,48; 1010,84</t>
+          <t>-30,68; —</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,31</t>
+          <t>2,55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,29</t>
+          <t>-0,61</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>1,34</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,89; 6,08</t>
+          <t>1,79; 5,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,45</t>
+          <t>0,29; 3,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,62</t>
+          <t>0,69; 4,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 0,76</t>
+          <t>-3,62; 0,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 2,02</t>
+          <t>-2,47; 1,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 0,46</t>
+          <t>-2,75; 2,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,36</t>
+          <t>0,45; 3,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,34</t>
+          <t>-0,21; 2,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 2,44</t>
+          <t>0,02; 3,04</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>298,45%</t>
+          <t>328,59%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-55,41%</t>
+          <t>-26,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>86,04; 2381,91</t>
+          <t>56,6; 2157,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1243,49</t>
+          <t>-9,22; 1150,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,18; 2159,64</t>
+          <t>14,28; 1652,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-89,84; 124,0</t>
+          <t>-91,63; 77,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-70,12; 187,79</t>
+          <t>-68,24; 190,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-89,0; 65,79</t>
+          <t>-79,61; 276,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,7; 407,55</t>
+          <t>16,11; 412,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-19,54; 306,19</t>
+          <t>-16,28; 303,55</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-26,72; 297,43</t>
+          <t>-2,29; 403,6</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>1,18</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,04</t>
+          <t>1,21; 3,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,12</t>
+          <t>0,59; 2,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,17</t>
+          <t>0,58; 2,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,44</t>
+          <t>-1,33; 0,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,86</t>
+          <t>-0,9; 0,86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,36</t>
+          <t>-0,21; 2,18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,88</t>
+          <t>0,54; 1,89</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,42</t>
+          <t>0,29; 1,4</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,54</t>
+          <t>0,54; 2,02</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>140,34%</t>
+          <t>165,45%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>132,93%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>92,96; 543,63</t>
+          <t>101,96; 595,01</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>38,4; 393,79</t>
+          <t>50,35; 435,98</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20,03; 366,01</t>
+          <t>37,56; 446,91</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-78,24; 100,15</t>
+          <t>-79,42; 105,04</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-61,33; 169,78</t>
+          <t>-59,05; 180,05</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-52,38; 214,67</t>
+          <t>-21,99; 358,46</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>48,87; 288,83</t>
+          <t>38,84; 276,78</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>16,6; 224,96</t>
+          <t>20,33; 213,81</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5,96; 229,3</t>
+          <t>43,76; 311,91</t>
         </is>
       </c>
     </row>
